--- a/Analysis/RAG_Ablation/rag_ablation_posthoc_tests.xlsx
+++ b/Analysis/RAG_Ablation/rag_ablation_posthoc_tests.xlsx
@@ -466,22 +466,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>control_k3</t>
+          <t>random_exemplars_k3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>random_exemplars_k3</t>
+          <t>retrieval_k5</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>51</v>
+        <v>659</v>
       </c>
       <c r="D2" t="n">
-        <v>2.04064417630434e-06</v>
+        <v>2.311695474859448e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.4644897959183674</v>
+        <v>0.3464197530864198</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -489,10 +489,10 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H2" t="n">
-        <v>5.713803693652153e-05</v>
+        <v>6.472747329606453e-07</v>
       </c>
       <c r="I2" t="b">
         <v>1</v>
@@ -501,22 +501,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>exemplars_no_hidden_params</t>
+          <t>descriptions_no_scores_ranks</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>random_exemplars_k3</t>
+          <t>nearest_neighbor_k3</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>73</v>
+        <v>701</v>
       </c>
       <c r="D3" t="n">
-        <v>2.156151458621025e-05</v>
+        <v>6.030415511057013e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.4220408163265306</v>
+        <v>0.3508641975308642</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -524,10 +524,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005821608938276768</v>
+        <v>1.628212187985394e-06</v>
       </c>
       <c r="I3" t="b">
         <v>1</v>
@@ -536,7 +536,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>random_exemplars_k3</t>
+          <t>descriptions_no_scores_ranks</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -545,13 +545,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>83</v>
+        <v>719</v>
       </c>
       <c r="D4" t="n">
-        <v>5.452072946354747e-05</v>
+        <v>9.018246027925301e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>0.436734693877551</v>
+        <v>0.3502469135802469</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -559,10 +559,10 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001417538966052234</v>
+        <v>2.344743967260578e-06</v>
       </c>
       <c r="I4" t="b">
         <v>1</v>
@@ -571,7 +571,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>alternate_embedding_k3</t>
+          <t>nearest_neighbor_k3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -580,13 +580,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>86</v>
+        <v>724</v>
       </c>
       <c r="D5" t="n">
-        <v>7.098051719367504e-05</v>
+        <v>1.007576677738998e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4220408163265306</v>
+        <v>-0.3461728395061728</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001774512929841876</v>
+        <v>2.518941694347496e-06</v>
       </c>
       <c r="I5" t="b">
         <v>1</v>
@@ -606,7 +606,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>nearest_neighbor_k3</t>
+          <t>control_k3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -615,24 +615,24 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>91</v>
+        <v>744</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001086841220967472</v>
+        <v>1.563854920220479e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4138775510204082</v>
+        <v>-0.3262962962962963</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>small</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002608418930321932</v>
+        <v>3.753251808529149e-06</v>
       </c>
       <c r="I6" t="b">
         <v>1</v>
@@ -641,33 +641,33 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>random_exemplars_k3</t>
+          <t>control_k3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>retrieval_k1</t>
+          <t>descriptions_no_scores_ranks</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>92</v>
+        <v>754</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001181175466626883</v>
+        <v>1.943660194534001e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3942857142857143</v>
+        <v>-0.3264197530864197</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>small</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00271670357324183</v>
+        <v>4.470418447428202e-06</v>
       </c>
       <c r="I7" t="b">
         <v>1</v>
@@ -676,22 +676,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>alternate_embedding_k3</t>
+          <t>exemplars_no_hidden_params</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>descriptions_no_scores_ranks</t>
+          <t>random_exemplars_k3</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>116</v>
+        <v>821</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0007301834993995726</v>
+        <v>8.012641568105803e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3061224489795918</v>
+        <v>-0.3217283950617284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0160640369867906</v>
+        <v>1.762781144983277e-05</v>
       </c>
       <c r="I8" t="b">
         <v>1</v>
@@ -711,33 +711,33 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>control_k3</t>
+          <t>descriptions_no_scores_ranks</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>descriptions_no_scores_ranks</t>
+          <t>exemplars_no_hidden_params</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>121</v>
+        <v>827</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001027080113999546</v>
+        <v>9.065139517022994e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3583673469387755</v>
+        <v>0.3172839506172839</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>small</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H9" t="n">
-        <v>0.02156868239399046</v>
+        <v>1.903679298574829e-05</v>
       </c>
       <c r="I9" t="b">
         <v>1</v>
@@ -746,22 +746,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>descriptions_no_scores_ranks</t>
+          <t>alternate_embedding_k3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>retrieval_k5</t>
+          <t>random_exemplars_k3</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>129</v>
+        <v>951.5</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00173009600257501</v>
+        <v>1.033840655026301e-05</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2914285714285714</v>
+        <v>-0.3019753086419753</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0346019200515002</v>
+        <v>0.0002067681310052601</v>
       </c>
       <c r="I10" t="b">
         <v>1</v>
@@ -781,22 +781,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>descriptions_no_scores_ranks</t>
+          <t>random_exemplars_k3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>exemplars_no_hidden_params</t>
+          <t>retrieval_k1</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>141</v>
+        <v>966</v>
       </c>
       <c r="D11" t="n">
-        <v>0.00358851789496839</v>
+        <v>1.351356831927695e-05</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2979591836734694</v>
+        <v>0.2733333333333333</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -804,34 +804,34 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H11" t="n">
-        <v>0.06818184000439942</v>
+        <v>0.0002567577980662621</v>
       </c>
       <c r="I11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>alternate_embedding_k3</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>descriptions_no_scores_ranks</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>nearest_neighbor_k3</t>
-        </is>
-      </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>1103</v>
       </c>
       <c r="D12" t="n">
-        <v>0.007811892894096673</v>
+        <v>0.0001444755909887869</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2424489795918367</v>
+        <v>-0.2819753086419753</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -839,13 +839,13 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1406140720937401</v>
+        <v>0.002600560637798164</v>
       </c>
       <c r="I12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -860,13 +860,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>156</v>
+        <v>1166</v>
       </c>
       <c r="D13" t="n">
-        <v>0.008234890352468938</v>
+        <v>0.000389819645803625</v>
       </c>
       <c r="E13" t="n">
-        <v>0.28</v>
+        <v>0.252716049382716</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -874,45 +874,45 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1399931359919719</v>
+        <v>0.006626933978661625</v>
       </c>
       <c r="I13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>descriptions_no_scores_ranks</t>
+          <t>retrieval_k1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>random_exemplars_k3</t>
+          <t>retrieval_k5</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>211</v>
+        <v>1540</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0902152419439517</v>
+        <v>0.04114934330920565</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1640816326530612</v>
+        <v>0.1151851851851852</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>negligible</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0.6583894929472904</v>
       </c>
       <c r="I14" t="b">
         <v>0</v>
@@ -926,17 +926,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>retrieval_k5</t>
+          <t>retrieval_k1</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>229</v>
+        <v>1571</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1633099506725557</v>
+        <v>0.05520139091222214</v>
       </c>
       <c r="E15" t="n">
-        <v>0.05795918367346939</v>
+        <v>-0.1007407407407407</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0.8280208636833322</v>
       </c>
       <c r="I15" t="b">
         <v>0</v>
@@ -965,13 +965,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>236</v>
+        <v>1615.5</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2011792931589298</v>
+        <v>0.1541298577943814</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.06612244897959184</v>
+        <v>-0.08864197530864197</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
@@ -991,22 +991,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>control_k3</t>
+          <t>exemplars_no_hidden_params</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nearest_neighbor_k3</t>
+          <t>retrieval_k5</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>263</v>
+        <v>1629</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4035886574420147</v>
+        <v>0.1710238126064378</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.07755102040816327</v>
+        <v>0.04506172839506173</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H17" t="n">
         <v>1</v>
@@ -1026,22 +1026,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>exemplars_no_hidden_params</t>
+          <t>alternate_embedding_k3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>retrieval_k1</t>
+          <t>nearest_neighbor_k3</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>267.5</v>
+        <v>1751</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4365558451870238</v>
+        <v>0.2328600816499938</v>
       </c>
       <c r="E18" t="n">
-        <v>0.007346938775510204</v>
+        <v>0.05444444444444444</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H18" t="n">
         <v>1</v>
@@ -1061,22 +1061,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>control_k3</t>
+          <t>exemplars_no_hidden_params</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>exemplars_no_hidden_params</t>
+          <t>retrieval_k1</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>240</v>
+        <v>1754</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4692824295985791</v>
+        <v>0.2376215306105461</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.05387755102040816</v>
+        <v>-0.07567901234567902</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H19" t="n">
         <v>1</v>
@@ -1096,7 +1096,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>retrieval_k1</t>
+          <t>alternate_embedding_k3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>272</v>
+        <v>1754</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4910651647369377</v>
+        <v>0.3092996512753813</v>
       </c>
       <c r="E20" t="n">
-        <v>0.01714285714285714</v>
+        <v>0.06802469135802469</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H20" t="n">
         <v>1</v>
@@ -1140,13 +1140,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>281</v>
+        <v>1834</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5875575871323235</v>
+        <v>0.3903087627616869</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0563265306122449</v>
+        <v>0.02518518518518519</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
@@ -1166,22 +1166,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>alternate_embedding_k3</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>exemplars_no_hidden_params</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>retrieval_k5</t>
-        </is>
-      </c>
       <c r="C22" t="n">
-        <v>280.5</v>
+        <v>1760.5</v>
       </c>
       <c r="D22" t="n">
-        <v>0.7713220240637385</v>
+        <v>0.4112078803063057</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.00326530612244898</v>
+        <v>0.02469135802469136</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H22" t="n">
         <v>1</v>
@@ -1210,13 +1210,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>297</v>
+        <v>1687</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7771179727860726</v>
+        <v>0.4294393811101025</v>
       </c>
       <c r="E23" t="n">
-        <v>0.05877551020408163</v>
+        <v>0.04740740740740741</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H23" t="n">
         <v>1</v>
@@ -1236,22 +1236,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>alternate_embedding_k3</t>
+          <t>control_k3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nearest_neighbor_k3</t>
+          <t>retrieval_k5</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>298</v>
+        <v>1733</v>
       </c>
       <c r="D24" t="n">
-        <v>0.7895531054819003</v>
+        <v>0.4436385985357695</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.05959183673469388</v>
+        <v>0.02185185185185185</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H24" t="n">
         <v>1</v>
@@ -1271,22 +1271,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>control_k3</t>
+          <t>alternate_embedding_k3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>retrieval_k5</t>
+          <t>retrieval_k1</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>275</v>
+        <v>1858.5</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9217139122894957</v>
+        <v>0.4469684848996611</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.03102040816326531</v>
+        <v>-0.05493827160493827</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H25" t="n">
         <v>1</v>
@@ -1306,22 +1306,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>alternate_embedding_k3</t>
+          <t>descriptions_no_scores_ranks</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>retrieval_k5</t>
+          <t>random_exemplars_k3</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>312</v>
+        <v>1902</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9677533526555635</v>
+        <v>0.6809420548816354</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.02857142857142857</v>
+        <v>-0.01271604938271605</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H26" t="n">
         <v>1</v>
@@ -1346,17 +1346,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>retrieval_k1</t>
+          <t>retrieval_k5</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>312</v>
+        <v>1949</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9677533526555635</v>
+        <v>0.6918591310155648</v>
       </c>
       <c r="E27" t="n">
-        <v>0.03346938775510204</v>
+        <v>0.004320987654320987</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H27" t="n">
         <v>1</v>
@@ -1376,7 +1376,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>alternate_embedding_k3</t>
+          <t>control_k3</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1385,13 +1385,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>313</v>
+        <v>1854</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9806487238383852</v>
+        <v>0.7995388663899359</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.02040816326530612</v>
+        <v>-0.01629629629629629</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H28" t="n">
         <v>1</v>
@@ -1411,22 +1411,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>alternate_embedding_k3</t>
+          <t>control_k3</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>retrieval_k1</t>
+          <t>nearest_neighbor_k3</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>313</v>
+        <v>2006</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9806487238383852</v>
+        <v>0.8673833586008021</v>
       </c>
       <c r="E29" t="n">
-        <v>0.005714285714285714</v>
+        <v>0.01679012345679012</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9806487238383852</v>
+        <v>0.8673833586008021</v>
       </c>
       <c r="I29" t="b">
         <v>0</v>
@@ -1446,33 +1446,33 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>control_k3</t>
+          <t>random_exemplars_k3</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>random_exemplars_k3</t>
+          <t>retrieval_k5</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>51</v>
+        <v>715</v>
       </c>
       <c r="D30" t="n">
-        <v>2.04064417630434e-06</v>
+        <v>8.250388456455381e-08</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.4840816326530612</v>
+        <v>0.3422222222222222</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H30" t="n">
-        <v>5.713803693652153e-05</v>
+        <v>2.310108767807507e-06</v>
       </c>
       <c r="I30" t="b">
         <v>1</v>
@@ -1481,33 +1481,33 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>control_k3</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>random_exemplars_k3</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>retrieval_k5</t>
-        </is>
-      </c>
       <c r="C31" t="n">
-        <v>74</v>
+        <v>769</v>
       </c>
       <c r="D31" t="n">
-        <v>2.374127507209778e-05</v>
+        <v>2.685400077977858e-07</v>
       </c>
       <c r="E31" t="n">
-        <v>0.4302040816326531</v>
+        <v>-0.3182716049382716</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>small</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H31" t="n">
-        <v>0.00064101442694664</v>
+        <v>7.250580210540216e-06</v>
       </c>
       <c r="I31" t="b">
         <v>1</v>
@@ -1516,7 +1516,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>exemplars_no_hidden_params</t>
+          <t>nearest_neighbor_k3</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1525,13 +1525,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>76</v>
+        <v>786</v>
       </c>
       <c r="D32" t="n">
-        <v>2.871413016691804e-05</v>
+        <v>3.856997694310567e-07</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4302040816326531</v>
+        <v>-0.3419753086419753</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1539,10 +1539,10 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H32" t="n">
-        <v>0.000746567384339869</v>
+        <v>1.002819400520747e-05</v>
       </c>
       <c r="I32" t="b">
         <v>1</v>
@@ -1551,22 +1551,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>nearest_neighbor_k3</t>
+          <t>descriptions_no_scores_ranks</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>random_exemplars_k3</t>
+          <t>retrieval_k5</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>77</v>
+        <v>791</v>
       </c>
       <c r="D33" t="n">
-        <v>3.15406359732151e-05</v>
+        <v>4.286690208878086e-07</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.433469387755102</v>
+        <v>0.3350617283950617</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0007885158993303776</v>
+        <v>1.071672552219522e-05</v>
       </c>
       <c r="I33" t="b">
         <v>1</v>
@@ -1586,22 +1586,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>random_exemplars_k3</t>
+          <t>descriptions_no_scores_ranks</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>retrieval_k1</t>
+          <t>nearest_neighbor_k3</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>80</v>
+        <v>796</v>
       </c>
       <c r="D34" t="n">
-        <v>4.160823300480843e-05</v>
+        <v>4.762386955461986e-07</v>
       </c>
       <c r="E34" t="n">
-        <v>0.4253061224489796</v>
+        <v>0.3350617283950617</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0009985975921154022</v>
+        <v>1.142972869310876e-05</v>
       </c>
       <c r="I34" t="b">
         <v>1</v>
@@ -1621,7 +1621,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>alternate_embedding_k3</t>
+          <t>exemplars_no_hidden_params</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1630,24 +1630,24 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>81</v>
+        <v>814</v>
       </c>
       <c r="D35" t="n">
-        <v>4.556449130177498e-05</v>
+        <v>6.933392804612371e-07</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.4204081632653061</v>
+        <v>-0.3106172839506173</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>small</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H35" t="n">
-        <v>0.001047983299940825</v>
+        <v>1.594680345060846e-05</v>
       </c>
       <c r="I35" t="b">
         <v>1</v>
@@ -1656,33 +1656,33 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>control_k3</t>
+          <t>descriptions_no_scores_ranks</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>descriptions_no_scores_ranks</t>
+          <t>exemplars_no_hidden_params</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>108</v>
+        <v>842</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0004121505771763623</v>
+        <v>1.231153512472356e-06</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.3779591836734694</v>
+        <v>0.3007407407407408</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>small</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H36" t="n">
-        <v>0.00906731269787997</v>
+        <v>2.708537727439184e-05</v>
       </c>
       <c r="I36" t="b">
         <v>1</v>
@@ -1691,22 +1691,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>control_k3</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
           <t>descriptions_no_scores_ranks</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>retrieval_k5</t>
-        </is>
-      </c>
       <c r="C37" t="n">
-        <v>123</v>
+        <v>859</v>
       </c>
       <c r="D37" t="n">
-        <v>0.001173330354504287</v>
+        <v>1.734266269654586e-06</v>
       </c>
       <c r="E37" t="n">
-        <v>0.2946938775510204</v>
+        <v>-0.2992592592592593</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H37" t="n">
-        <v>0.02463993744459003</v>
+        <v>3.64195916627463e-05</v>
       </c>
       <c r="I37" t="b">
         <v>1</v>
@@ -1731,17 +1731,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>descriptions_no_scores_ranks</t>
+          <t>random_exemplars_k3</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>124</v>
+        <v>870</v>
       </c>
       <c r="D38" t="n">
-        <v>0.001253210823051631</v>
+        <v>2.159511979085273e-06</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.2979591836734694</v>
+        <v>-0.3158024691358025</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H38" t="n">
-        <v>0.02506421646103263</v>
+        <v>4.319023958170547e-05</v>
       </c>
       <c r="I38" t="b">
         <v>1</v>
@@ -1761,22 +1761,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>descriptions_no_scores_ranks</t>
+          <t>random_exemplars_k3</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>exemplars_no_hidden_params</t>
+          <t>retrieval_k1</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>134</v>
+        <v>1018</v>
       </c>
       <c r="D39" t="n">
-        <v>0.002362151222769171</v>
+        <v>3.43708821240952e-05</v>
       </c>
       <c r="E39" t="n">
-        <v>0.3093877551020408</v>
+        <v>0.2508641975308642</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1784,10 +1784,10 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H39" t="n">
-        <v>0.04488087323261425</v>
+        <v>0.0006530467603578088</v>
       </c>
       <c r="I39" t="b">
         <v>1</v>
@@ -1796,22 +1796,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>alternate_embedding_k3</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>descriptions_no_scores_ranks</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>retrieval_k1</t>
-        </is>
-      </c>
       <c r="C40" t="n">
-        <v>137</v>
+        <v>1039</v>
       </c>
       <c r="D40" t="n">
-        <v>0.002832830476108938</v>
+        <v>4.951805069600684e-05</v>
       </c>
       <c r="E40" t="n">
-        <v>0.2995918367346939</v>
+        <v>-0.2893827160493827</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1819,13 +1819,13 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H40" t="n">
-        <v>0.05099094856996089</v>
+        <v>0.0008913249125281231</v>
       </c>
       <c r="I40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -1836,17 +1836,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nearest_neighbor_k3</t>
+          <t>retrieval_k1</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>143</v>
+        <v>1212</v>
       </c>
       <c r="D41" t="n">
-        <v>0.004029071831610054</v>
+        <v>0.0007743843754613966</v>
       </c>
       <c r="E41" t="n">
-        <v>0.2718367346938775</v>
+        <v>0.2266666666666667</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1854,19 +1854,19 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H41" t="n">
-        <v>0.06849422113737091</v>
+        <v>0.01316453438284374</v>
       </c>
       <c r="I41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>nearest_neighbor_k3</t>
+          <t>retrieval_k1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1875,13 +1875,13 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>231</v>
+        <v>1534</v>
       </c>
       <c r="D42" t="n">
-        <v>0.173550461535342</v>
+        <v>0.03881297877997977</v>
       </c>
       <c r="E42" t="n">
-        <v>0.06448979591836734</v>
+        <v>0.1138271604938272</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>0.6210076604796764</v>
       </c>
       <c r="I42" t="b">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>descriptions_no_scores_ranks</t>
+          <t>nearest_neighbor_k3</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>random_exemplars_k3</t>
+          <t>retrieval_k1</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>235</v>
+        <v>1565</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1954178527230397</v>
+        <v>0.05220616193572072</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.1379591836734694</v>
+        <v>-0.1049382716049383</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>0.7830924290358108</v>
       </c>
       <c r="I43" t="b">
         <v>0</v>
@@ -1936,22 +1936,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>control_k3</t>
+          <t>exemplars_no_hidden_params</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>retrieval_k1</t>
+          <t>retrieval_k5</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>246</v>
+        <v>1618</v>
       </c>
       <c r="D44" t="n">
-        <v>0.2654948046547361</v>
+        <v>0.1571591385125046</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.03510204081632653</v>
+        <v>0.04679012345679012</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H44" t="n">
         <v>1</v>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>nearest_neighbor_k3</t>
+          <t>retrieval_k1</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>272</v>
+        <v>1710</v>
       </c>
       <c r="D45" t="n">
-        <v>0.4910651647369377</v>
+        <v>0.1744652818400637</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.07918367346938776</v>
+        <v>-0.08814814814814814</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H45" t="n">
         <v>1</v>
@@ -2006,22 +2006,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>exemplars_no_hidden_params</t>
+          <t>alternate_embedding_k3</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>nearest_neighbor_k3</t>
+          <t>retrieval_k1</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>272</v>
+        <v>1721</v>
       </c>
       <c r="D46" t="n">
-        <v>0.4910651647369377</v>
+        <v>0.1889356042203602</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.05306122448979592</v>
+        <v>-0.0745679012345679</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H46" t="n">
         <v>1</v>
@@ -2041,7 +2041,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>retrieval_k1</t>
+          <t>control_k3</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2050,13 +2050,13 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>283</v>
+        <v>1613</v>
       </c>
       <c r="D47" t="n">
-        <v>0.6101043444359675</v>
+        <v>0.2026814001985868</v>
       </c>
       <c r="E47" t="n">
-        <v>0.02040816326530612</v>
+        <v>0.02839506172839506</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H47" t="n">
         <v>1</v>
@@ -2085,13 +2085,13 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>285</v>
+        <v>1734</v>
       </c>
       <c r="D48" t="n">
-        <v>0.6330176034243777</v>
+        <v>0.2071552494076608</v>
       </c>
       <c r="E48" t="n">
-        <v>0.01551020408163265</v>
+        <v>-0.07654320987654321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H48" t="n">
         <v>1</v>
@@ -2111,22 +2111,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>control_k3</t>
+          <t>alternate_embedding_k3</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>exemplars_no_hidden_params</t>
+          <t>nearest_neighbor_k3</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>273</v>
+        <v>1836</v>
       </c>
       <c r="D49" t="n">
-        <v>0.6753150747875152</v>
+        <v>0.3947636989431871</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.04897959183673469</v>
+        <v>0.04271604938271605</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H49" t="n">
         <v>1</v>
@@ -2151,17 +2151,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>retrieval_k5</t>
+          <t>nearest_neighbor_k3</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>274</v>
+        <v>1838</v>
       </c>
       <c r="D50" t="n">
-        <v>0.6878546970101984</v>
+        <v>0.3992492488532766</v>
       </c>
       <c r="E50" t="n">
-        <v>0.00163265306122449</v>
+        <v>0.0291358024691358</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H50" t="n">
         <v>1</v>
@@ -2186,17 +2186,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>control_k3</t>
+          <t>retrieval_k5</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>299</v>
+        <v>1819</v>
       </c>
       <c r="D51" t="n">
-        <v>0.8020407048752531</v>
+        <v>0.4527994056646476</v>
       </c>
       <c r="E51" t="n">
-        <v>0.06285714285714286</v>
+        <v>0.05296296296296296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H51" t="n">
         <v>1</v>
@@ -2216,22 +2216,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>alternate_embedding_k3</t>
+          <t>nearest_neighbor_k3</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>retrieval_k1</t>
+          <t>retrieval_k5</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>306</v>
+        <v>1919</v>
       </c>
       <c r="D52" t="n">
-        <v>0.8906679842039011</v>
+        <v>0.6051254378966182</v>
       </c>
       <c r="E52" t="n">
-        <v>0.02204081632653061</v>
+        <v>0.006913580246913581</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H52" t="n">
         <v>1</v>
@@ -2251,22 +2251,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>nearest_neighbor_k3</t>
+          <t>descriptions_no_scores_ranks</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>retrieval_k1</t>
+          <t>random_exemplars_k3</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>308</v>
+        <v>1926</v>
       </c>
       <c r="D53" t="n">
-        <v>0.9162867379491217</v>
+        <v>0.6249279392503635</v>
       </c>
       <c r="E53" t="n">
-        <v>0.03020408163265306</v>
+        <v>-0.01753086419753086</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H53" t="n">
         <v>1</v>
@@ -2286,7 +2286,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>alternate_embedding_k3</t>
+          <t>control_k3</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2295,13 +2295,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>310</v>
+        <v>1958</v>
       </c>
       <c r="D54" t="n">
-        <v>0.9419905297108926</v>
+        <v>0.7187572875862429</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.04</v>
+        <v>0.03308641975308642</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H54" t="n">
         <v>1</v>
@@ -2321,22 +2321,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>control_k3</t>
+          <t>alternate_embedding_k3</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>retrieval_k5</t>
+          <t>exemplars_no_hidden_params</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>278</v>
+        <v>1874</v>
       </c>
       <c r="D55" t="n">
-        <v>0.9643706868158897</v>
+        <v>0.7267050582614414</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.04653061224489796</v>
+        <v>0.008271604938271605</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H55" t="n">
         <v>1</v>
@@ -2361,17 +2361,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>exemplars_no_hidden_params</t>
+          <t>control_k3</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>313</v>
+        <v>1820</v>
       </c>
       <c r="D56" t="n">
-        <v>0.9806487238383852</v>
+        <v>0.8278554513826153</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.01551020408163265</v>
+        <v>0.02160493827160494</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H56" t="n">
         <v>1</v>
@@ -2391,22 +2391,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>alternate_embedding_k3</t>
+          <t>control_k3</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>retrieval_k5</t>
+          <t>exemplars_no_hidden_params</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>314</v>
+        <v>1912</v>
       </c>
       <c r="D57" t="n">
-        <v>0.9935490260832012</v>
+        <v>0.9932461640894359</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.01061224489795918</v>
+        <v>-0.009753086419753086</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="H57" t="n">
-        <v>0.9935490260832012</v>
+        <v>0.9932461640894359</v>
       </c>
       <c r="I57" t="b">
         <v>0</v>

--- a/Analysis/RAG_Ablation/rag_ablation_posthoc_tests.xlsx
+++ b/Analysis/RAG_Ablation/rag_ablation_posthoc_tests.xlsx
@@ -413,51 +413,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:J57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>config_i</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>config_j</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>statistic</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>cliff_delta</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>cliff_delta_interpretation</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>n_pairs</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>p_holm</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>significant_holm</t>
         </is>
@@ -466,1960 +471,2240 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>random_exemplars_k3</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>retrieval_k5</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>659</v>
-      </c>
       <c r="D2" t="n">
-        <v>2.311695474859448e-08</v>
+        <v>658</v>
       </c>
       <c r="E2" t="n">
+        <v>2.258754031054112e-08</v>
+      </c>
+      <c r="F2" t="n">
         <v>0.3464197530864198</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>90</v>
-      </c>
       <c r="H2" t="n">
-        <v>6.472747329606453e-07</v>
-      </c>
-      <c r="I2" t="b">
+        <v>90</v>
+      </c>
+      <c r="I2" t="n">
+        <v>6.324511286951513e-07</v>
+      </c>
+      <c r="J2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>descriptions_no_scores_ranks</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>nearest_neighbor_k3</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>701</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>6.030415511057013e-08</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>0.3508641975308642</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>90</v>
-      </c>
       <c r="H3" t="n">
+        <v>90</v>
+      </c>
+      <c r="I3" t="n">
         <v>1.628212187985394e-06</v>
       </c>
-      <c r="I3" t="b">
+      <c r="J3" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>descriptions_no_scores_ranks</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>retrieval_k5</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>719</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>9.018246027925301e-08</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>0.3502469135802469</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>90</v>
-      </c>
       <c r="H4" t="n">
+        <v>90</v>
+      </c>
+      <c r="I4" t="n">
         <v>2.344743967260578e-06</v>
       </c>
-      <c r="I4" t="b">
+      <c r="J4" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>nearest_neighbor_k3</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>random_exemplars_k3</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>724</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>1.007576677738998e-07</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>-0.3461728395061728</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>90</v>
-      </c>
       <c r="H5" t="n">
+        <v>90</v>
+      </c>
+      <c r="I5" t="n">
         <v>2.518941694347496e-06</v>
       </c>
-      <c r="I5" t="b">
+      <c r="J5" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>control_k3</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>random_exemplars_k3</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>744</v>
-      </c>
       <c r="D6" t="n">
-        <v>1.563854920220479e-07</v>
+        <v>744.5</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3262962962962963</v>
-      </c>
-      <c r="F6" t="inlineStr">
+        <v>1.580963967037341e-07</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.3261728395061728</v>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>small</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>90</v>
-      </c>
       <c r="H6" t="n">
-        <v>3.753251808529149e-06</v>
-      </c>
-      <c r="I6" t="b">
+        <v>90</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.794313520889617e-06</v>
+      </c>
+      <c r="J6" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>control_k3</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>descriptions_no_scores_ranks</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>754</v>
       </c>
-      <c r="D7" t="n">
-        <v>1.943660194534001e-07</v>
-      </c>
       <c r="E7" t="n">
+        <v>1.943715314174502e-07</v>
+      </c>
+      <c r="F7" t="n">
         <v>-0.3264197530864197</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>small</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>90</v>
-      </c>
       <c r="H7" t="n">
-        <v>4.470418447428202e-06</v>
-      </c>
-      <c r="I7" t="b">
+        <v>90</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.470545222601354e-06</v>
+      </c>
+      <c r="J7" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>exemplars_no_hidden_params</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>random_exemplars_k3</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>821</v>
       </c>
-      <c r="D8" t="n">
-        <v>8.012641568105803e-07</v>
-      </c>
       <c r="E8" t="n">
+        <v>8.012846583727678e-07</v>
+      </c>
+      <c r="F8" t="n">
         <v>-0.3217283950617284</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>small</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>90</v>
-      </c>
       <c r="H8" t="n">
-        <v>1.762781144983277e-05</v>
-      </c>
-      <c r="I8" t="b">
+        <v>90</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.762826248420089e-05</v>
+      </c>
+      <c r="J8" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>descriptions_no_scores_ranks</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>exemplars_no_hidden_params</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>827</v>
-      </c>
       <c r="D9" t="n">
-        <v>9.065139517022994e-07</v>
+        <v>826</v>
       </c>
       <c r="E9" t="n">
+        <v>8.881153485340396e-07</v>
+      </c>
+      <c r="F9" t="n">
         <v>0.3172839506172839</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>small</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>90</v>
-      </c>
       <c r="H9" t="n">
-        <v>1.903679298574829e-05</v>
-      </c>
-      <c r="I9" t="b">
+        <v>90</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.865042231921483e-05</v>
+      </c>
+      <c r="J9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>alternate_embedding_k3</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>random_exemplars_k3</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>951.5</v>
-      </c>
       <c r="D10" t="n">
-        <v>1.033840655026301e-05</v>
+        <v>952</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3019753086419753</v>
-      </c>
-      <c r="F10" t="inlineStr">
+        <v>1.043531144271831e-05</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.3020987654320988</v>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>small</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>90</v>
-      </c>
       <c r="H10" t="n">
-        <v>0.0002067681310052601</v>
-      </c>
-      <c r="I10" t="b">
+        <v>90</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.0002087062288543661</v>
+      </c>
+      <c r="J10" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>random_exemplars_k3</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>retrieval_k1</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>966</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>1.351356831927695e-05</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>0.2733333333333333</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>small</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>90</v>
-      </c>
       <c r="H11" t="n">
+        <v>90</v>
+      </c>
+      <c r="I11" t="n">
         <v>0.0002567577980662621</v>
       </c>
-      <c r="I11" t="b">
+      <c r="J11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>alternate_embedding_k3</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>descriptions_no_scores_ranks</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>1103</v>
       </c>
-      <c r="D12" t="n">
-        <v>0.0001444755909887869</v>
-      </c>
       <c r="E12" t="n">
-        <v>-0.2819753086419753</v>
-      </c>
-      <c r="F12" t="inlineStr">
+        <v>0.0001444778331620556</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.2820987654320988</v>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>small</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>90</v>
-      </c>
       <c r="H12" t="n">
-        <v>0.002600560637798164</v>
-      </c>
-      <c r="I12" t="b">
+        <v>90</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.002600600996917001</v>
+      </c>
+      <c r="J12" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>descriptions_no_scores_ranks</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>retrieval_k1</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>1166</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>0.000389819645803625</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>0.252716049382716</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>small</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>90</v>
-      </c>
       <c r="H13" t="n">
+        <v>90</v>
+      </c>
+      <c r="I13" t="n">
         <v>0.006626933978661625</v>
       </c>
-      <c r="I13" t="b">
+      <c r="J13" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>retrieval_k1</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>retrieval_k5</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>1540</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>0.04114934330920565</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>0.1151851851851852</v>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>90</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
       </c>
       <c r="H14" t="n">
+        <v>90</v>
+      </c>
+      <c r="I14" t="n">
         <v>0.6583894929472904</v>
       </c>
-      <c r="I14" t="b">
+      <c r="J14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>nearest_neighbor_k3</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>retrieval_k1</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>1571</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>0.05520139091222214</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>-0.1007407407407407</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>90</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
       </c>
       <c r="H15" t="n">
+        <v>90</v>
+      </c>
+      <c r="I15" t="n">
         <v>0.8280208636833322</v>
       </c>
-      <c r="I15" t="b">
+      <c r="J15" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>control_k3</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>retrieval_k1</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>1615.5</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>0.1541298577943814</v>
       </c>
-      <c r="E16" t="n">
-        <v>-0.08864197530864197</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>90</v>
+      <c r="F16" t="n">
+        <v>-0.08851851851851852</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" t="b">
+        <v>90</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>exemplars_no_hidden_params</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>retrieval_k5</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>1629</v>
-      </c>
       <c r="D17" t="n">
-        <v>0.1710238126064378</v>
+        <v>1630</v>
       </c>
       <c r="E17" t="n">
+        <v>0.1723282903232224</v>
+      </c>
+      <c r="F17" t="n">
         <v>0.04506172839506173</v>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>90</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" t="b">
+        <v>90</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>alternate_embedding_k3</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>nearest_neighbor_k3</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>1751</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>0.2328600816499938</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>0.05444444444444444</v>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>90</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" t="b">
+        <v>90</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>exemplars_no_hidden_params</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>retrieval_k1</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>1754</v>
-      </c>
       <c r="D19" t="n">
-        <v>0.2376215306105461</v>
+        <v>1714</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.07567901234567902</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>90</v>
+        <v>0.2378633512926176</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-0.07580246913580246</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" t="b">
+        <v>90</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>alternate_embedding_k3</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>retrieval_k5</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="D20" t="n">
         <v>1754</v>
       </c>
-      <c r="D20" t="n">
-        <v>0.3092996512753813</v>
-      </c>
       <c r="E20" t="n">
+        <v>0.3092986389736464</v>
+      </c>
+      <c r="F20" t="n">
         <v>0.06802469135802469</v>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>90</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" t="b">
+        <v>90</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>exemplars_no_hidden_params</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>nearest_neighbor_k3</t>
         </is>
       </c>
-      <c r="C21" t="n">
-        <v>1834</v>
-      </c>
       <c r="D21" t="n">
-        <v>0.3903087627616869</v>
+        <v>1836</v>
       </c>
       <c r="E21" t="n">
+        <v>0.3947632205972523</v>
+      </c>
+      <c r="F21" t="n">
         <v>0.02518518518518519</v>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>90</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" t="b">
+        <v>90</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>alternate_embedding_k3</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>exemplars_no_hidden_params</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>1760.5</v>
-      </c>
       <c r="D22" t="n">
-        <v>0.4112078803063057</v>
+        <v>1759</v>
       </c>
       <c r="E22" t="n">
+        <v>0.40766468242733</v>
+      </c>
+      <c r="F22" t="n">
         <v>0.02469135802469136</v>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>90</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" t="b">
+        <v>90</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>alternate_embedding_k3</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>control_k3</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>1687</v>
-      </c>
       <c r="D23" t="n">
-        <v>0.4294393811101025</v>
+        <v>1688</v>
       </c>
       <c r="E23" t="n">
-        <v>0.04740740740740741</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>90</v>
+        <v>0.4319580927071868</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.04728395061728395</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" t="b">
+        <v>90</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>control_k3</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>retrieval_k5</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="D24" t="n">
         <v>1733</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
         <v>0.4436385985357695</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>0.02185185185185185</v>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>90</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" t="b">
+        <v>90</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>alternate_embedding_k3</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>retrieval_k1</t>
         </is>
       </c>
-      <c r="C25" t="n">
-        <v>1858.5</v>
-      </c>
       <c r="D25" t="n">
-        <v>0.4469684848996611</v>
+        <v>1861</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.05493827160493827</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>90</v>
+        <v>0.4530030183687184</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.05481481481481482</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" t="b">
+        <v>90</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>descriptions_no_scores_ranks</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>random_exemplars_k3</t>
         </is>
       </c>
-      <c r="C26" t="n">
-        <v>1902</v>
-      </c>
       <c r="D26" t="n">
-        <v>0.6809420548816354</v>
+        <v>1904.5</v>
       </c>
       <c r="E26" t="n">
+        <v>0.688457198987484</v>
+      </c>
+      <c r="F26" t="n">
         <v>-0.01271604938271605</v>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>90</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" t="b">
+        <v>90</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>nearest_neighbor_k3</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>retrieval_k5</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="D27" t="n">
         <v>1949</v>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
         <v>0.6918591310155648</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>0.004320987654320987</v>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>90</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" t="b">
+        <v>90</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>control_k3</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>exemplars_no_hidden_params</t>
         </is>
       </c>
-      <c r="C28" t="n">
-        <v>1854</v>
-      </c>
       <c r="D28" t="n">
-        <v>0.7995388663899359</v>
+        <v>1856</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.01629629629629629</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>90</v>
+        <v>0.8060856677094397</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-0.01604938271604938</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" t="b">
+        <v>90</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>control_k3</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>nearest_neighbor_k3</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="D29" t="n">
         <v>2006</v>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
         <v>0.8673833586008021</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>0.01679012345679012</v>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>90</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
       </c>
       <c r="H29" t="n">
+        <v>90</v>
+      </c>
+      <c r="I29" t="n">
         <v>0.8673833586008021</v>
       </c>
-      <c r="I29" t="b">
+      <c r="J29" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>score_rmse</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>random_exemplars_k3</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>retrieval_k5</t>
         </is>
       </c>
-      <c r="C30" t="n">
+      <c r="D30" t="n">
         <v>715</v>
       </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
         <v>8.250388456455381e-08</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>0.3422222222222222</v>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>90</v>
-      </c>
       <c r="H30" t="n">
+        <v>90</v>
+      </c>
+      <c r="I30" t="n">
         <v>2.310108767807507e-06</v>
       </c>
-      <c r="I30" t="b">
+      <c r="J30" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>score_rmse</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>control_k3</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>random_exemplars_k3</t>
         </is>
       </c>
-      <c r="C31" t="n">
+      <c r="D31" t="n">
         <v>769</v>
       </c>
-      <c r="D31" t="n">
+      <c r="E31" t="n">
         <v>2.685400077977858e-07</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>-0.3182716049382716</v>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>small</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>90</v>
-      </c>
       <c r="H31" t="n">
+        <v>90</v>
+      </c>
+      <c r="I31" t="n">
         <v>7.250580210540216e-06</v>
       </c>
-      <c r="I31" t="b">
+      <c r="J31" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>score_rmse</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>nearest_neighbor_k3</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>random_exemplars_k3</t>
         </is>
       </c>
-      <c r="C32" t="n">
+      <c r="D32" t="n">
         <v>786</v>
       </c>
-      <c r="D32" t="n">
+      <c r="E32" t="n">
         <v>3.856997694310567e-07</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>-0.3419753086419753</v>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>90</v>
-      </c>
       <c r="H32" t="n">
+        <v>90</v>
+      </c>
+      <c r="I32" t="n">
         <v>1.002819400520747e-05</v>
       </c>
-      <c r="I32" t="b">
+      <c r="J32" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>score_rmse</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>descriptions_no_scores_ranks</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>retrieval_k5</t>
         </is>
       </c>
-      <c r="C33" t="n">
+      <c r="D33" t="n">
         <v>791</v>
       </c>
-      <c r="D33" t="n">
+      <c r="E33" t="n">
         <v>4.286690208878086e-07</v>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>0.3350617283950617</v>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>90</v>
-      </c>
       <c r="H33" t="n">
+        <v>90</v>
+      </c>
+      <c r="I33" t="n">
         <v>1.071672552219522e-05</v>
       </c>
-      <c r="I33" t="b">
+      <c r="J33" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>score_rmse</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>descriptions_no_scores_ranks</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>nearest_neighbor_k3</t>
         </is>
       </c>
-      <c r="C34" t="n">
+      <c r="D34" t="n">
         <v>796</v>
       </c>
-      <c r="D34" t="n">
+      <c r="E34" t="n">
         <v>4.762386955461986e-07</v>
       </c>
-      <c r="E34" t="n">
+      <c r="F34" t="n">
         <v>0.3350617283950617</v>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>90</v>
-      </c>
       <c r="H34" t="n">
+        <v>90</v>
+      </c>
+      <c r="I34" t="n">
         <v>1.142972869310876e-05</v>
       </c>
-      <c r="I34" t="b">
+      <c r="J34" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>score_rmse</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>exemplars_no_hidden_params</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>random_exemplars_k3</t>
         </is>
       </c>
-      <c r="C35" t="n">
+      <c r="D35" t="n">
         <v>814</v>
       </c>
-      <c r="D35" t="n">
+      <c r="E35" t="n">
         <v>6.933392804612371e-07</v>
       </c>
-      <c r="E35" t="n">
+      <c r="F35" t="n">
         <v>-0.3106172839506173</v>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>small</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>90</v>
-      </c>
       <c r="H35" t="n">
+        <v>90</v>
+      </c>
+      <c r="I35" t="n">
         <v>1.594680345060846e-05</v>
       </c>
-      <c r="I35" t="b">
+      <c r="J35" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>score_rmse</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>descriptions_no_scores_ranks</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>exemplars_no_hidden_params</t>
         </is>
       </c>
-      <c r="C36" t="n">
+      <c r="D36" t="n">
         <v>842</v>
       </c>
-      <c r="D36" t="n">
+      <c r="E36" t="n">
         <v>1.231153512472356e-06</v>
       </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
         <v>0.3007407407407408</v>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>small</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>90</v>
-      </c>
       <c r="H36" t="n">
+        <v>90</v>
+      </c>
+      <c r="I36" t="n">
         <v>2.708537727439184e-05</v>
       </c>
-      <c r="I36" t="b">
+      <c r="J36" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>score_rmse</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
           <t>control_k3</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>descriptions_no_scores_ranks</t>
         </is>
       </c>
-      <c r="C37" t="n">
+      <c r="D37" t="n">
         <v>859</v>
       </c>
-      <c r="D37" t="n">
+      <c r="E37" t="n">
         <v>1.734266269654586e-06</v>
       </c>
-      <c r="E37" t="n">
+      <c r="F37" t="n">
         <v>-0.2992592592592593</v>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>small</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>90</v>
-      </c>
       <c r="H37" t="n">
+        <v>90</v>
+      </c>
+      <c r="I37" t="n">
         <v>3.64195916627463e-05</v>
       </c>
-      <c r="I37" t="b">
+      <c r="J37" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>score_rmse</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>alternate_embedding_k3</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>random_exemplars_k3</t>
         </is>
       </c>
-      <c r="C38" t="n">
+      <c r="D38" t="n">
         <v>870</v>
       </c>
-      <c r="D38" t="n">
+      <c r="E38" t="n">
         <v>2.159511979085273e-06</v>
       </c>
-      <c r="E38" t="n">
+      <c r="F38" t="n">
         <v>-0.3158024691358025</v>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>small</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>90</v>
-      </c>
       <c r="H38" t="n">
+        <v>90</v>
+      </c>
+      <c r="I38" t="n">
         <v>4.319023958170547e-05</v>
       </c>
-      <c r="I38" t="b">
+      <c r="J38" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>score_rmse</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>random_exemplars_k3</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>retrieval_k1</t>
         </is>
       </c>
-      <c r="C39" t="n">
+      <c r="D39" t="n">
         <v>1018</v>
       </c>
-      <c r="D39" t="n">
+      <c r="E39" t="n">
         <v>3.43708821240952e-05</v>
       </c>
-      <c r="E39" t="n">
+      <c r="F39" t="n">
         <v>0.2508641975308642</v>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>small</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>90</v>
-      </c>
       <c r="H39" t="n">
+        <v>90</v>
+      </c>
+      <c r="I39" t="n">
         <v>0.0006530467603578088</v>
       </c>
-      <c r="I39" t="b">
+      <c r="J39" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>score_rmse</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>alternate_embedding_k3</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>descriptions_no_scores_ranks</t>
         </is>
       </c>
-      <c r="C40" t="n">
+      <c r="D40" t="n">
         <v>1039</v>
       </c>
-      <c r="D40" t="n">
+      <c r="E40" t="n">
         <v>4.951805069600684e-05</v>
       </c>
-      <c r="E40" t="n">
+      <c r="F40" t="n">
         <v>-0.2893827160493827</v>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>small</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>90</v>
-      </c>
       <c r="H40" t="n">
+        <v>90</v>
+      </c>
+      <c r="I40" t="n">
         <v>0.0008913249125281231</v>
       </c>
-      <c r="I40" t="b">
+      <c r="J40" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>score_rmse</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>descriptions_no_scores_ranks</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>retrieval_k1</t>
         </is>
       </c>
-      <c r="C41" t="n">
+      <c r="D41" t="n">
         <v>1212</v>
       </c>
-      <c r="D41" t="n">
+      <c r="E41" t="n">
         <v>0.0007743843754613966</v>
       </c>
-      <c r="E41" t="n">
+      <c r="F41" t="n">
         <v>0.2266666666666667</v>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>small</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>90</v>
-      </c>
       <c r="H41" t="n">
+        <v>90</v>
+      </c>
+      <c r="I41" t="n">
         <v>0.01316453438284374</v>
       </c>
-      <c r="I41" t="b">
+      <c r="J41" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>score_rmse</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>retrieval_k1</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>retrieval_k5</t>
         </is>
       </c>
-      <c r="C42" t="n">
+      <c r="D42" t="n">
         <v>1534</v>
       </c>
-      <c r="D42" t="n">
+      <c r="E42" t="n">
         <v>0.03881297877997977</v>
       </c>
-      <c r="E42" t="n">
+      <c r="F42" t="n">
         <v>0.1138271604938272</v>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
-        <v>90</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
       </c>
       <c r="H42" t="n">
+        <v>90</v>
+      </c>
+      <c r="I42" t="n">
         <v>0.6210076604796764</v>
       </c>
-      <c r="I42" t="b">
+      <c r="J42" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>score_rmse</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>nearest_neighbor_k3</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>retrieval_k1</t>
         </is>
       </c>
-      <c r="C43" t="n">
+      <c r="D43" t="n">
         <v>1565</v>
       </c>
-      <c r="D43" t="n">
+      <c r="E43" t="n">
         <v>0.05220616193572072</v>
       </c>
-      <c r="E43" t="n">
+      <c r="F43" t="n">
         <v>-0.1049382716049383</v>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="G43" t="n">
-        <v>90</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
       </c>
       <c r="H43" t="n">
+        <v>90</v>
+      </c>
+      <c r="I43" t="n">
         <v>0.7830924290358108</v>
       </c>
-      <c r="I43" t="b">
+      <c r="J43" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>score_rmse</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>exemplars_no_hidden_params</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>retrieval_k5</t>
         </is>
       </c>
-      <c r="C44" t="n">
+      <c r="D44" t="n">
         <v>1618</v>
       </c>
-      <c r="D44" t="n">
+      <c r="E44" t="n">
         <v>0.1571591385125046</v>
       </c>
-      <c r="E44" t="n">
+      <c r="F44" t="n">
         <v>0.04679012345679012</v>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="G44" t="n">
-        <v>90</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
-      </c>
-      <c r="I44" t="b">
+        <v>90</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>score_rmse</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
           <t>control_k3</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>retrieval_k1</t>
         </is>
       </c>
-      <c r="C45" t="n">
+      <c r="D45" t="n">
         <v>1710</v>
       </c>
-      <c r="D45" t="n">
+      <c r="E45" t="n">
         <v>0.1744652818400637</v>
       </c>
-      <c r="E45" t="n">
+      <c r="F45" t="n">
         <v>-0.08814814814814814</v>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="G45" t="n">
-        <v>90</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
       </c>
       <c r="H45" t="n">
-        <v>1</v>
-      </c>
-      <c r="I45" t="b">
+        <v>90</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>score_rmse</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>alternate_embedding_k3</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>retrieval_k1</t>
         </is>
       </c>
-      <c r="C46" t="n">
+      <c r="D46" t="n">
         <v>1721</v>
       </c>
-      <c r="D46" t="n">
+      <c r="E46" t="n">
         <v>0.1889356042203602</v>
       </c>
-      <c r="E46" t="n">
+      <c r="F46" t="n">
         <v>-0.0745679012345679</v>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="G46" t="n">
-        <v>90</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
-      </c>
-      <c r="I46" t="b">
+        <v>90</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>score_rmse</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>control_k3</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>retrieval_k5</t>
         </is>
       </c>
-      <c r="C47" t="n">
+      <c r="D47" t="n">
         <v>1613</v>
       </c>
-      <c r="D47" t="n">
+      <c r="E47" t="n">
         <v>0.2026814001985868</v>
       </c>
-      <c r="E47" t="n">
+      <c r="F47" t="n">
         <v>0.02839506172839506</v>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="G47" t="n">
-        <v>90</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
-      </c>
-      <c r="I47" t="b">
+        <v>90</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>score_rmse</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>exemplars_no_hidden_params</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>retrieval_k1</t>
         </is>
       </c>
-      <c r="C48" t="n">
+      <c r="D48" t="n">
         <v>1734</v>
       </c>
-      <c r="D48" t="n">
+      <c r="E48" t="n">
         <v>0.2071552494076608</v>
       </c>
-      <c r="E48" t="n">
+      <c r="F48" t="n">
         <v>-0.07654320987654321</v>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="G48" t="n">
-        <v>90</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
-      </c>
-      <c r="I48" t="b">
+        <v>90</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>score_rmse</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>alternate_embedding_k3</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>nearest_neighbor_k3</t>
         </is>
       </c>
-      <c r="C49" t="n">
+      <c r="D49" t="n">
         <v>1836</v>
       </c>
-      <c r="D49" t="n">
+      <c r="E49" t="n">
         <v>0.3947636989431871</v>
       </c>
-      <c r="E49" t="n">
+      <c r="F49" t="n">
         <v>0.04271604938271605</v>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="G49" t="n">
-        <v>90</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
       </c>
       <c r="H49" t="n">
-        <v>1</v>
-      </c>
-      <c r="I49" t="b">
+        <v>90</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>score_rmse</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
           <t>exemplars_no_hidden_params</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>nearest_neighbor_k3</t>
         </is>
       </c>
-      <c r="C50" t="n">
+      <c r="D50" t="n">
         <v>1838</v>
       </c>
-      <c r="D50" t="n">
+      <c r="E50" t="n">
         <v>0.3992492488532766</v>
       </c>
-      <c r="E50" t="n">
+      <c r="F50" t="n">
         <v>0.0291358024691358</v>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="G50" t="n">
-        <v>90</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
       </c>
       <c r="H50" t="n">
-        <v>1</v>
-      </c>
-      <c r="I50" t="b">
+        <v>90</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>score_rmse</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
           <t>alternate_embedding_k3</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>retrieval_k5</t>
         </is>
       </c>
-      <c r="C51" t="n">
+      <c r="D51" t="n">
         <v>1819</v>
       </c>
-      <c r="D51" t="n">
+      <c r="E51" t="n">
         <v>0.4527994056646476</v>
       </c>
-      <c r="E51" t="n">
+      <c r="F51" t="n">
         <v>0.05296296296296296</v>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="G51" t="n">
-        <v>90</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
       </c>
       <c r="H51" t="n">
-        <v>1</v>
-      </c>
-      <c r="I51" t="b">
+        <v>90</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>score_rmse</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>nearest_neighbor_k3</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>retrieval_k5</t>
         </is>
       </c>
-      <c r="C52" t="n">
+      <c r="D52" t="n">
         <v>1919</v>
       </c>
-      <c r="D52" t="n">
+      <c r="E52" t="n">
         <v>0.6051254378966182</v>
       </c>
-      <c r="E52" t="n">
+      <c r="F52" t="n">
         <v>0.006913580246913581</v>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="G52" t="n">
-        <v>90</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
       </c>
       <c r="H52" t="n">
-        <v>1</v>
-      </c>
-      <c r="I52" t="b">
+        <v>90</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>score_rmse</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
           <t>descriptions_no_scores_ranks</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>random_exemplars_k3</t>
         </is>
       </c>
-      <c r="C53" t="n">
+      <c r="D53" t="n">
         <v>1926</v>
       </c>
-      <c r="D53" t="n">
+      <c r="E53" t="n">
         <v>0.6249279392503635</v>
       </c>
-      <c r="E53" t="n">
+      <c r="F53" t="n">
         <v>-0.01753086419753086</v>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="G53" t="n">
-        <v>90</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
-      </c>
-      <c r="I53" t="b">
+        <v>90</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>score_rmse</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>control_k3</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>nearest_neighbor_k3</t>
         </is>
       </c>
-      <c r="C54" t="n">
+      <c r="D54" t="n">
         <v>1958</v>
       </c>
-      <c r="D54" t="n">
+      <c r="E54" t="n">
         <v>0.7187572875862429</v>
       </c>
-      <c r="E54" t="n">
+      <c r="F54" t="n">
         <v>0.03308641975308642</v>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="G54" t="n">
-        <v>90</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
-      </c>
-      <c r="I54" t="b">
+        <v>90</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>score_rmse</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
           <t>alternate_embedding_k3</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>exemplars_no_hidden_params</t>
         </is>
       </c>
-      <c r="C55" t="n">
+      <c r="D55" t="n">
         <v>1874</v>
       </c>
-      <c r="D55" t="n">
+      <c r="E55" t="n">
         <v>0.7267050582614414</v>
       </c>
-      <c r="E55" t="n">
+      <c r="F55" t="n">
         <v>0.008271604938271605</v>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="G55" t="n">
-        <v>90</v>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
       </c>
       <c r="H55" t="n">
-        <v>1</v>
-      </c>
-      <c r="I55" t="b">
+        <v>90</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>score_rmse</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
           <t>alternate_embedding_k3</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>control_k3</t>
         </is>
       </c>
-      <c r="C56" t="n">
+      <c r="D56" t="n">
         <v>1820</v>
       </c>
-      <c r="D56" t="n">
+      <c r="E56" t="n">
         <v>0.8278554513826153</v>
       </c>
-      <c r="E56" t="n">
+      <c r="F56" t="n">
         <v>0.02160493827160494</v>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="G56" t="n">
-        <v>90</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
       </c>
       <c r="H56" t="n">
-        <v>1</v>
-      </c>
-      <c r="I56" t="b">
+        <v>90</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>score_rmse</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
           <t>control_k3</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>exemplars_no_hidden_params</t>
         </is>
       </c>
-      <c r="C57" t="n">
+      <c r="D57" t="n">
         <v>1912</v>
       </c>
-      <c r="D57" t="n">
+      <c r="E57" t="n">
         <v>0.9932461640894359</v>
       </c>
-      <c r="E57" t="n">
+      <c r="F57" t="n">
         <v>-0.009753086419753086</v>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="G57" t="n">
-        <v>90</v>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
       </c>
       <c r="H57" t="n">
+        <v>90</v>
+      </c>
+      <c r="I57" t="n">
         <v>0.9932461640894359</v>
       </c>
-      <c r="I57" t="b">
+      <c r="J57" t="b">
         <v>0</v>
       </c>
     </row>
